--- a/data/software.xlsx
+++ b/data/software.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EF1A24-E140-4A4F-A3BE-37160E2CD1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E094B75-DA71-4A31-B089-C86A34C571BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="1290" windowWidth="28800" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="108">
   <si>
     <t>type</t>
   </si>
@@ -73,9 +73,6 @@
     <t>code for follow-up quantification</t>
   </si>
   <si>
-    <t>markdown</t>
-  </si>
-  <si>
     <t>webpage</t>
   </si>
   <si>
@@ -335,13 +332,25 @@
   </si>
   <si>
     <t>https://github.com/EBPI-Biostatistics/biostatUZH</t>
+  </si>
+  <si>
+    <t>https://oncoestimand.github.io/complex_designs_communication/complex_designs_communication.html</t>
+  </si>
+  <si>
+    <t>Communicating results in trials with multiple hypotheses or adaptive design features</t>
+  </si>
+  <si>
+    <t>https://github.com/oncoestimand/complex_designs_communication</t>
+  </si>
+  <si>
+    <t>quarto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +365,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,13 +393,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -668,24 +688,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="61.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultColWidth="61.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.1796875" style="1"/>
-    <col min="5" max="5" width="60.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="60.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="61.1796875" style="1"/>
+    <col min="4" max="4" width="61.140625" style="1"/>
+    <col min="5" max="5" width="60.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="60.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="61.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -714,507 +734,526 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>101</v>
+        <v>2026</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1">
         <v>2024</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="E4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1">
         <v>2024</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2023</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="K6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1">
         <v>2023</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>10</v>
+        <v>83</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C8" s="1">
         <v>2023</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="J9" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="1">
-        <v>2021</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="1">
-        <v>2020</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="C12" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C13" s="1">
         <v>2016</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2014</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="I15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2014</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2011</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C16" s="1">
         <v>2011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2011</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2010</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C18" s="1">
         <v>2010</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2009</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1">
         <v>2009</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2008</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="H23" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2007</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2006</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C24" s="1">
         <v>2006</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="K5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J2" r:id="rId6" xr:uid="{E29B216E-C4E5-43CE-989D-AD0C945DEA11}"/>
-    <hyperlink ref="E17" r:id="rId7" xr:uid="{14101D93-E0E3-4B7D-ADFB-DBD6AA712003}"/>
+    <hyperlink ref="K11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E18" r:id="rId6" xr:uid="{14101D93-E0E3-4B7D-ADFB-DBD6AA712003}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>